--- a/templates/template-excel-class.xlsx
+++ b/templates/template-excel-class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/se140866/code/work/teacher-management/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8913289-A3A4-4B59-97F7-0871D364D29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462500AE-E3B6-8740-BF41-22489056C896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B86C3D59-9088-4750-8AD3-CC752ED3B4D9}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29040" windowHeight="16440" xr2:uid="{B86C3D59-9088-4750-8AD3-CC752ED3B4D9}"/>
   </bookViews>
   <sheets>
     <sheet name="KẾT QUẢ LỚP" sheetId="2" r:id="rId1"/>
@@ -70,7 +70,7 @@
         <sz val="13"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">             </t>
@@ -82,7 +82,7 @@
         <sz val="13"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Độc lập - Tự do - Hạnh Phúc</t>
@@ -111,7 +111,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,7 +123,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -131,7 +131,7 @@
       <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -140,7 +140,7 @@
       <sz val="13"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -245,14 +245,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -623,60 +623,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9984EBA0-A49D-46E2-AF4D-7F82E3A2CD36}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="19.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25">
+    <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
       <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" ht="17.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
       <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10">
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="7" t="str">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="str">
         <f xml:space="preserve"> "KỲ THI ĐÁNH GIÁ HỌC KỲ II - NĂM HỌC: 2025 2026 
 BẢNG ĐIỂM HỌC SINH K6
 TRƯỜNG: " &amp; data!B1 &amp; CHAR(10) &amp;
@@ -686,53 +686,53 @@
 TRƯỜNG: abc
 LỚP: 123</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:10" ht="56.1" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" ht="51.75">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -762,7 +762,7 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
     </row>
@@ -782,12 +782,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16585AF8-85A2-441B-9CAB-7600676698E6}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -795,7 +795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
